--- a/artfynd/A 10166-2023 artfynd.xlsx
+++ b/artfynd/A 10166-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596301</v>
+        <v>122596302</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>806421</v>
+        <v>806364</v>
       </c>
       <c r="R2" t="n">
-        <v>7429262</v>
+        <v>7429309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596302</v>
+        <v>122596301</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>92113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>806364</v>
+        <v>806421</v>
       </c>
       <c r="R3" t="n">
-        <v>7429309</v>
+        <v>7429262</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 10166-2023 artfynd.xlsx
+++ b/artfynd/A 10166-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>122596301</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 10166-2023 artfynd.xlsx
+++ b/artfynd/A 10166-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596301</v>
+        <v>122596302</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>806421</v>
+        <v>806364</v>
       </c>
       <c r="R2" t="n">
-        <v>7429262</v>
+        <v>7429309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596302</v>
+        <v>122596301</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>806364</v>
+        <v>806421</v>
       </c>
       <c r="R3" t="n">
-        <v>7429309</v>
+        <v>7429262</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 10166-2023 artfynd.xlsx
+++ b/artfynd/A 10166-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596302</v>
+        <v>122596301</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>806364</v>
+        <v>806421</v>
       </c>
       <c r="R2" t="n">
-        <v>7429309</v>
+        <v>7429262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596301</v>
+        <v>122596302</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>806421</v>
+        <v>806364</v>
       </c>
       <c r="R3" t="n">
-        <v>7429262</v>
+        <v>7429309</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 10166-2023 artfynd.xlsx
+++ b/artfynd/A 10166-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122596301</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
